--- a/tests.xlsx
+++ b/tests.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NAL\code\HTSims_GIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Aditya_Intern\codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB88CDB-D70B-4B85-86C7-B166C0FD6B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="tests_8nodes" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="data" sheetId="2" r:id="rId3"/>
     <sheet name="ht paths" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="144">
   <si>
     <t>Battery Front</t>
   </si>
@@ -432,16 +431,49 @@
     <t>4m/s</t>
   </si>
   <si>
-    <t>Result 2 – Effect of internal forced convection</t>
-  </si>
-  <si>
     <t>As we can observe there is a decrease in temp of every component especially esc as that component has the most surface area exposed to internal air which then leads to a decrease in the temp of esc mount too</t>
+  </si>
+  <si>
+    <t>Result 3 – Effect of internal forced convection</t>
+  </si>
+  <si>
+    <t>Initial Temperature: 225 K (-48.1C),</t>
+  </si>
+  <si>
+    <t>Ambient temperature: 219.7K (-53.5C) (Temp at alt 23 km)</t>
+  </si>
+  <si>
+    <t>ESC Power output : 60 W</t>
+  </si>
+  <si>
+    <t>Check 4 – Temperature analysis at 23 km altitude w reduced ESC Heat generation</t>
+  </si>
+  <si>
+    <t>11m/s</t>
+  </si>
+  <si>
+    <t>As we can observe there is a decrease in temp of every component as the ambient temp reduces significantly even though convection stops playing a huge part of external heat dissipation, we also see forced convection is very helpful in our case to shed heat off</t>
+  </si>
+  <si>
+    <t>Initial Temperature: 242.7 K (-30.5C),</t>
+  </si>
+  <si>
+    <t>Ambient temperature: 245K (-28.1C) (Temp at alt 7 km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As we can observe there is a decrease in temp of every component at no velocity compared to the 23 km case due to the density of air being almost 10x the 23km case leading to natural convection showing effect even at 0 m/s but in case of forced convection it is more effective at 23kms solely due to the ambient temperature difference </t>
+  </si>
+  <si>
+    <t>Check 5 – Temperature analysis at 7 km altitude w reduced ESC Heat generation</t>
+  </si>
+  <si>
+    <t>Check 6 – Temperature analysis at 0.125 km altitude w reduced ESC Heat generation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1008,35 +1040,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P182"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="84.88671875" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.6640625" customWidth="1"/>
-    <col min="16" max="16" width="21.44140625" customWidth="1"/>
-    <col min="17" max="17" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="84.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E2" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E3" s="8" t="s">
         <v>111</v>
       </c>
@@ -1052,7 +1084,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
@@ -1072,7 +1104,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>19</v>
       </c>
@@ -1111,7 +1143,7 @@
       </c>
       <c r="P5" s="38"/>
     </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35"/>
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
@@ -1138,7 +1170,7 @@
       <c r="O6" s="39"/>
       <c r="P6" s="40"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="35"/>
       <c r="B7" s="35"/>
       <c r="C7" s="35"/>
@@ -1177,7 +1209,7 @@
       <c r="O7" s="39"/>
       <c r="P7" s="40"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
       <c r="B8" s="35"/>
       <c r="C8" s="35"/>
@@ -1216,7 +1248,7 @@
       <c r="O8" s="39"/>
       <c r="P8" s="40"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
@@ -1255,7 +1287,7 @@
       <c r="O9" s="39"/>
       <c r="P9" s="40"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="35"/>
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
@@ -1294,7 +1326,7 @@
       <c r="O10" s="39"/>
       <c r="P10" s="40"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="35"/>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
@@ -1333,7 +1365,7 @@
       <c r="O11" s="39"/>
       <c r="P11" s="40"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1369,7 +1401,7 @@
       <c r="O12" s="39"/>
       <c r="P12" s="40"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E13" s="3" t="s">
         <v>6</v>
       </c>
@@ -1405,7 +1437,7 @@
       <c r="O13" s="39"/>
       <c r="P13" s="40"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E14" s="3" t="s">
         <v>7</v>
       </c>
@@ -1441,7 +1473,7 @@
       <c r="O14" s="39"/>
       <c r="P14" s="40"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1477,12 +1509,12 @@
       <c r="O15" s="39"/>
       <c r="P15" s="40"/>
     </row>
-    <row r="18" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E18" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E19" s="8" t="s">
         <v>21</v>
       </c>
@@ -1498,7 +1530,7 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E20" s="6" t="s">
         <v>15</v>
       </c>
@@ -1518,7 +1550,7 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>16</v>
       </c>
@@ -1557,7 +1589,7 @@
       </c>
       <c r="P21" s="38"/>
     </row>
-    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="35"/>
       <c r="B22" s="35"/>
       <c r="C22" s="35"/>
@@ -1584,7 +1616,7 @@
       <c r="O22" s="39"/>
       <c r="P22" s="40"/>
     </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="35"/>
       <c r="B23" s="35"/>
       <c r="C23" s="35"/>
@@ -1623,7 +1655,7 @@
       <c r="O23" s="39"/>
       <c r="P23" s="40"/>
     </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="35"/>
       <c r="B24" s="35"/>
       <c r="C24" s="35"/>
@@ -1662,7 +1694,7 @@
       <c r="O24" s="39"/>
       <c r="P24" s="40"/>
     </row>
-    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="35"/>
       <c r="B25" s="35"/>
       <c r="C25" s="35"/>
@@ -1701,7 +1733,7 @@
       <c r="O25" s="39"/>
       <c r="P25" s="40"/>
     </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="35"/>
       <c r="B26" s="35"/>
       <c r="C26" s="35"/>
@@ -1740,7 +1772,7 @@
       <c r="O26" s="39"/>
       <c r="P26" s="40"/>
     </row>
-    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="35"/>
       <c r="B27" s="35"/>
       <c r="C27" s="35"/>
@@ -1779,7 +1811,7 @@
       <c r="O27" s="39"/>
       <c r="P27" s="40"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E28" s="3" t="s">
         <v>5</v>
       </c>
@@ -1815,7 +1847,7 @@
       <c r="O28" s="39"/>
       <c r="P28" s="40"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E29" s="3" t="s">
         <v>6</v>
       </c>
@@ -1851,7 +1883,7 @@
       <c r="O29" s="39"/>
       <c r="P29" s="40"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E30" s="3" t="s">
         <v>7</v>
       </c>
@@ -1887,7 +1919,7 @@
       <c r="O30" s="39"/>
       <c r="P30" s="40"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E31" s="3" t="s">
         <v>8</v>
       </c>
@@ -1923,12 +1955,12 @@
       <c r="O31" s="39"/>
       <c r="P31" s="40"/>
     </row>
-    <row r="34" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E34" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E35" s="8" t="s">
         <v>21</v>
       </c>
@@ -1944,7 +1976,7 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
     </row>
-    <row r="36" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E36" s="6" t="s">
         <v>15</v>
       </c>
@@ -1964,7 +1996,7 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="35" t="s">
         <v>23</v>
       </c>
@@ -2003,7 +2035,7 @@
       </c>
       <c r="P37" s="38"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="35"/>
       <c r="B38" s="35"/>
       <c r="C38" s="35"/>
@@ -2030,7 +2062,7 @@
       <c r="O38" s="39"/>
       <c r="P38" s="40"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="35"/>
       <c r="B39" s="35"/>
       <c r="C39" s="35"/>
@@ -2069,7 +2101,7 @@
       <c r="O39" s="39"/>
       <c r="P39" s="40"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" s="35"/>
       <c r="C40" s="35"/>
@@ -2108,7 +2140,7 @@
       <c r="O40" s="39"/>
       <c r="P40" s="40"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="35"/>
       <c r="B41" s="35"/>
       <c r="C41" s="35"/>
@@ -2147,7 +2179,7 @@
       <c r="O41" s="39"/>
       <c r="P41" s="40"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35"/>
@@ -2186,7 +2218,7 @@
       <c r="O42" s="39"/>
       <c r="P42" s="40"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="35"/>
       <c r="B43" s="35"/>
       <c r="C43" s="35"/>
@@ -2225,7 +2257,7 @@
       <c r="O43" s="39"/>
       <c r="P43" s="40"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2261,7 +2293,7 @@
       <c r="O44" s="39"/>
       <c r="P44" s="40"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E45" s="3" t="s">
         <v>6</v>
       </c>
@@ -2297,7 +2329,7 @@
       <c r="O45" s="39"/>
       <c r="P45" s="40"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E46" s="3" t="s">
         <v>7</v>
       </c>
@@ -2333,7 +2365,7 @@
       <c r="O46" s="39"/>
       <c r="P46" s="40"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2369,17 +2401,17 @@
       <c r="O47" s="39"/>
       <c r="P47" s="40"/>
     </row>
-    <row r="50" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E50" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E51" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E52" s="8" t="s">
         <v>28</v>
       </c>
@@ -2395,7 +2427,7 @@
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
     </row>
-    <row r="53" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E53" s="6" t="s">
         <v>15</v>
       </c>
@@ -2415,7 +2447,7 @@
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
         <v>26</v>
       </c>
@@ -2454,7 +2486,7 @@
       </c>
       <c r="P54" s="38"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="35"/>
       <c r="B55" s="35"/>
       <c r="C55" s="35"/>
@@ -2481,7 +2513,7 @@
       <c r="O55" s="39"/>
       <c r="P55" s="40"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="35"/>
       <c r="B56" s="35"/>
       <c r="C56" s="35"/>
@@ -2520,7 +2552,7 @@
       <c r="O56" s="39"/>
       <c r="P56" s="40"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="35"/>
       <c r="B57" s="35"/>
       <c r="C57" s="35"/>
@@ -2559,7 +2591,7 @@
       <c r="O57" s="39"/>
       <c r="P57" s="40"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="35"/>
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
@@ -2598,7 +2630,7 @@
       <c r="O58" s="39"/>
       <c r="P58" s="40"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="35"/>
       <c r="B59" s="35"/>
       <c r="C59" s="35"/>
@@ -2637,7 +2669,7 @@
       <c r="O59" s="39"/>
       <c r="P59" s="40"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="35"/>
       <c r="B60" s="35"/>
       <c r="C60" s="35"/>
@@ -2676,7 +2708,7 @@
       <c r="O60" s="39"/>
       <c r="P60" s="40"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E61" s="3" t="s">
         <v>5</v>
       </c>
@@ -2712,7 +2744,7 @@
       <c r="O61" s="39"/>
       <c r="P61" s="40"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E62" s="3" t="s">
         <v>6</v>
       </c>
@@ -2748,7 +2780,7 @@
       <c r="O62" s="39"/>
       <c r="P62" s="40"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E63" s="3" t="s">
         <v>7</v>
       </c>
@@ -2784,7 +2816,7 @@
       <c r="O63" s="39"/>
       <c r="P63" s="40"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E64" s="3" t="s">
         <v>8</v>
       </c>
@@ -2820,17 +2852,17 @@
       <c r="O64" s="39"/>
       <c r="P64" s="40"/>
     </row>
-    <row r="67" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E67" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E68" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E69" s="8" t="s">
         <v>28</v>
       </c>
@@ -2846,7 +2878,7 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
     </row>
-    <row r="70" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E70" s="6" t="s">
         <v>36</v>
       </c>
@@ -2866,7 +2898,7 @@
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="35" t="s">
         <v>34</v>
       </c>
@@ -2905,7 +2937,7 @@
       </c>
       <c r="P71" s="38"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="35"/>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
@@ -2932,7 +2964,7 @@
       <c r="O72" s="39"/>
       <c r="P72" s="40"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="35"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -2971,7 +3003,7 @@
       <c r="O73" s="39"/>
       <c r="P73" s="40"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="35"/>
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
@@ -3010,7 +3042,7 @@
       <c r="O74" s="39"/>
       <c r="P74" s="40"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="35"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -3049,7 +3081,7 @@
       <c r="O75" s="39"/>
       <c r="P75" s="40"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="35"/>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
@@ -3088,7 +3120,7 @@
       <c r="O76" s="39"/>
       <c r="P76" s="40"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="35"/>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
@@ -3127,7 +3159,7 @@
       <c r="O77" s="39"/>
       <c r="P77" s="40"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E78" s="3" t="s">
         <v>5</v>
       </c>
@@ -3163,7 +3195,7 @@
       <c r="O78" s="39"/>
       <c r="P78" s="40"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E79" s="3" t="s">
         <v>6</v>
       </c>
@@ -3199,7 +3231,7 @@
       <c r="O79" s="39"/>
       <c r="P79" s="40"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E80" s="3" t="s">
         <v>7</v>
       </c>
@@ -3235,7 +3267,7 @@
       <c r="O80" s="39"/>
       <c r="P80" s="40"/>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E81" s="3" t="s">
         <v>8</v>
       </c>
@@ -3271,17 +3303,17 @@
       <c r="O81" s="39"/>
       <c r="P81" s="40"/>
     </row>
-    <row r="84" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E84" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E85" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E86" s="8" t="s">
         <v>28</v>
       </c>
@@ -3297,7 +3329,7 @@
       <c r="O86" s="1"/>
       <c r="P86" s="1"/>
     </row>
-    <row r="87" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E87" s="8" t="s">
         <v>35</v>
       </c>
@@ -3313,7 +3345,7 @@
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
     </row>
-    <row r="88" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E88" s="6" t="s">
         <v>36</v>
       </c>
@@ -3333,7 +3365,7 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="35" t="s">
         <v>33</v>
       </c>
@@ -3372,7 +3404,7 @@
       </c>
       <c r="P89" s="38"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="35"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35"/>
@@ -3399,7 +3431,7 @@
       <c r="O90" s="39"/>
       <c r="P90" s="40"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="35"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35"/>
@@ -3438,7 +3470,7 @@
       <c r="O91" s="39"/>
       <c r="P91" s="40"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="35"/>
       <c r="B92" s="35"/>
       <c r="C92" s="35"/>
@@ -3477,7 +3509,7 @@
       <c r="O92" s="39"/>
       <c r="P92" s="40"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="35"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35"/>
@@ -3516,7 +3548,7 @@
       <c r="O93" s="39"/>
       <c r="P93" s="40"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35"/>
@@ -3555,7 +3587,7 @@
       <c r="O94" s="39"/>
       <c r="P94" s="40"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35"/>
@@ -3594,7 +3626,7 @@
       <c r="O95" s="39"/>
       <c r="P95" s="40"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E96" s="3" t="s">
         <v>5</v>
       </c>
@@ -3630,7 +3662,7 @@
       <c r="O96" s="39"/>
       <c r="P96" s="40"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E97" s="3" t="s">
         <v>6</v>
       </c>
@@ -3666,7 +3698,7 @@
       <c r="O97" s="39"/>
       <c r="P97" s="40"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E98" s="3" t="s">
         <v>7</v>
       </c>
@@ -3702,7 +3734,7 @@
       <c r="O98" s="39"/>
       <c r="P98" s="40"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E99" s="3" t="s">
         <v>8</v>
       </c>
@@ -3738,17 +3770,17 @@
       <c r="O99" s="39"/>
       <c r="P99" s="40"/>
     </row>
-    <row r="102" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E102" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E103" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E104" s="6" t="s">
         <v>15</v>
       </c>
@@ -3766,7 +3798,7 @@
       <c r="O104" s="1"/>
       <c r="P104" s="1"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="35" t="s">
         <v>41</v>
       </c>
@@ -3805,7 +3837,7 @@
       </c>
       <c r="P105" s="38"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="35"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35"/>
@@ -3832,7 +3864,7 @@
       <c r="O106" s="39"/>
       <c r="P106" s="40"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35"/>
@@ -3871,7 +3903,7 @@
       <c r="O107" s="39"/>
       <c r="P107" s="40"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35"/>
@@ -3910,7 +3942,7 @@
       <c r="O108" s="39"/>
       <c r="P108" s="40"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35"/>
@@ -3949,7 +3981,7 @@
       <c r="O109" s="39"/>
       <c r="P109" s="40"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="35"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
@@ -3988,7 +4020,7 @@
       <c r="O110" s="39"/>
       <c r="P110" s="40"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="35"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35"/>
@@ -4027,7 +4059,7 @@
       <c r="O111" s="39"/>
       <c r="P111" s="40"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E112" s="3" t="s">
         <v>5</v>
       </c>
@@ -4063,7 +4095,7 @@
       <c r="O112" s="39"/>
       <c r="P112" s="40"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E113" s="3" t="s">
         <v>6</v>
       </c>
@@ -4099,7 +4131,7 @@
       <c r="O113" s="39"/>
       <c r="P113" s="40"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E114" s="3" t="s">
         <v>7</v>
       </c>
@@ -4135,7 +4167,7 @@
       <c r="O114" s="39"/>
       <c r="P114" s="40"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E115" s="3" t="s">
         <v>8</v>
       </c>
@@ -4171,22 +4203,22 @@
       <c r="O115" s="39"/>
       <c r="P115" s="40"/>
     </row>
-    <row r="119" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E119" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E120" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E121" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E122" s="8" t="s">
         <v>13</v>
       </c>
@@ -4202,7 +4234,7 @@
       <c r="O122" s="1"/>
       <c r="P122" s="1"/>
     </row>
-    <row r="123" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E123" s="6" t="s">
         <v>15</v>
       </c>
@@ -4222,7 +4254,7 @@
       <c r="O123" s="1"/>
       <c r="P123" s="1"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="35" t="s">
         <v>19</v>
       </c>
@@ -4261,7 +4293,7 @@
       </c>
       <c r="P124" s="38"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="35"/>
       <c r="B125" s="35"/>
       <c r="C125" s="35"/>
@@ -4290,7 +4322,7 @@
       </c>
       <c r="P125" s="40"/>
     </row>
-    <row r="126" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="35"/>
       <c r="B126" s="35"/>
       <c r="C126" s="35"/>
@@ -4329,7 +4361,7 @@
       <c r="O126" s="39"/>
       <c r="P126" s="40"/>
     </row>
-    <row r="127" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="35"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35"/>
@@ -4368,7 +4400,7 @@
       <c r="O127" s="39"/>
       <c r="P127" s="40"/>
     </row>
-    <row r="128" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="35"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
@@ -4407,7 +4439,7 @@
       <c r="O128" s="39"/>
       <c r="P128" s="40"/>
     </row>
-    <row r="129" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="35"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35"/>
@@ -4444,7 +4476,7 @@
       <c r="O129" s="39"/>
       <c r="P129" s="40"/>
     </row>
-    <row r="130" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="35"/>
       <c r="B130" s="35"/>
       <c r="C130" s="35"/>
@@ -4483,7 +4515,7 @@
       <c r="O130" s="39"/>
       <c r="P130" s="40"/>
     </row>
-    <row r="131" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="35"/>
       <c r="B131" s="35"/>
       <c r="C131" s="35"/>
@@ -4522,7 +4554,7 @@
       <c r="O131" s="39"/>
       <c r="P131" s="40"/>
     </row>
-    <row r="132" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E132" s="3" t="s">
         <v>5</v>
       </c>
@@ -4558,7 +4590,7 @@
       <c r="O132" s="39"/>
       <c r="P132" s="40"/>
     </row>
-    <row r="133" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E133" s="3" t="s">
         <v>6</v>
       </c>
@@ -4594,7 +4626,7 @@
       <c r="O133" s="39"/>
       <c r="P133" s="40"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E134" s="3" t="s">
         <v>7</v>
       </c>
@@ -4630,7 +4662,7 @@
       <c r="O134" s="39"/>
       <c r="P134" s="40"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E135" s="3" t="s">
         <v>8</v>
       </c>
@@ -4666,10 +4698,10 @@
       <c r="O135" s="39"/>
       <c r="P135" s="40"/>
     </row>
-    <row r="138" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E138" s="7"/>
     </row>
-    <row r="139" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E139" s="9" t="s">
         <v>66</v>
       </c>
@@ -4686,7 +4718,7 @@
       <c r="M139" s="34"/>
       <c r="N139" s="34"/>
     </row>
-    <row r="140" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E140" s="9" t="s">
         <v>17</v>
       </c>
@@ -4699,7 +4731,7 @@
       <c r="M140" s="34"/>
       <c r="N140" s="34"/>
     </row>
-    <row r="141" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E141" s="8" t="s">
         <v>67</v>
       </c>
@@ -4715,7 +4747,7 @@
       <c r="O141" s="1"/>
       <c r="P141" s="1"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="35" t="s">
         <v>65</v>
       </c>
@@ -4754,7 +4786,7 @@
       </c>
       <c r="P142" s="38"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="35"/>
       <c r="B143" s="35"/>
       <c r="C143" s="35"/>
@@ -4781,7 +4813,7 @@
       <c r="O143" s="39"/>
       <c r="P143" s="40"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="35"/>
       <c r="B144" s="35"/>
       <c r="C144" s="35"/>
@@ -4820,7 +4852,7 @@
       <c r="O144" s="39"/>
       <c r="P144" s="40"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="35"/>
       <c r="B145" s="35"/>
       <c r="C145" s="35"/>
@@ -4859,7 +4891,7 @@
       <c r="O145" s="39"/>
       <c r="P145" s="40"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="35"/>
       <c r="B146" s="35"/>
       <c r="C146" s="35"/>
@@ -4898,7 +4930,7 @@
       <c r="O146" s="39"/>
       <c r="P146" s="40"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="35"/>
       <c r="B147" s="35"/>
       <c r="C147" s="35"/>
@@ -4935,7 +4967,7 @@
       <c r="O147" s="39"/>
       <c r="P147" s="40"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="35"/>
       <c r="B148" s="35"/>
       <c r="C148" s="35"/>
@@ -4974,7 +5006,7 @@
       <c r="O148" s="39"/>
       <c r="P148" s="40"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="35"/>
       <c r="B149" s="35"/>
       <c r="C149" s="35"/>
@@ -5013,7 +5045,7 @@
       <c r="O149" s="39"/>
       <c r="P149" s="40"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E150" s="3" t="s">
         <v>5</v>
       </c>
@@ -5049,7 +5081,7 @@
       <c r="O150" s="39"/>
       <c r="P150" s="40"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E151" s="3" t="s">
         <v>6</v>
       </c>
@@ -5085,7 +5117,7 @@
       <c r="O151" s="39"/>
       <c r="P151" s="40"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E152" s="3" t="s">
         <v>7</v>
       </c>
@@ -5121,7 +5153,7 @@
       <c r="O152" s="39"/>
       <c r="P152" s="40"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E153" s="3" t="s">
         <v>8</v>
       </c>
@@ -5157,7 +5189,7 @@
       <c r="O153" s="39"/>
       <c r="P153" s="40"/>
     </row>
-    <row r="156" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E156" s="9" t="s">
         <v>66</v>
       </c>
@@ -5174,7 +5206,7 @@
       <c r="M156" s="34"/>
       <c r="N156" s="34"/>
     </row>
-    <row r="157" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E157" s="9" t="s">
         <v>17</v>
       </c>
@@ -5187,7 +5219,7 @@
       <c r="M157" s="34"/>
       <c r="N157" s="34"/>
     </row>
-    <row r="158" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E158" s="8" t="s">
         <v>67</v>
       </c>
@@ -5203,7 +5235,7 @@
       <c r="O158" s="1"/>
       <c r="P158" s="1"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="35" t="s">
         <v>74</v>
       </c>
@@ -5234,7 +5266,7 @@
       </c>
       <c r="P159" s="38"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="35"/>
       <c r="B160" s="35"/>
       <c r="C160" s="35"/>
@@ -5257,7 +5289,7 @@
       <c r="O160" s="39"/>
       <c r="P160" s="40"/>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="35"/>
       <c r="B161" s="35"/>
       <c r="C161" s="35"/>
@@ -5286,7 +5318,7 @@
       <c r="O161" s="39"/>
       <c r="P161" s="40"/>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="35"/>
       <c r="B162" s="35"/>
       <c r="C162" s="35"/>
@@ -5315,7 +5347,7 @@
       <c r="O162" s="39"/>
       <c r="P162" s="40"/>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="35"/>
       <c r="B163" s="35"/>
       <c r="C163" s="35"/>
@@ -5344,7 +5376,7 @@
       <c r="O163" s="39"/>
       <c r="P163" s="40"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="35"/>
       <c r="B164" s="35"/>
       <c r="C164" s="35"/>
@@ -5372,7 +5404,7 @@
       <c r="O164" s="39"/>
       <c r="P164" s="40"/>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="35"/>
       <c r="B165" s="35"/>
       <c r="C165" s="35"/>
@@ -5401,7 +5433,7 @@
       <c r="O165" s="39"/>
       <c r="P165" s="40"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="35"/>
       <c r="B166" s="35"/>
       <c r="C166" s="35"/>
@@ -5430,7 +5462,7 @@
       <c r="O166" s="39"/>
       <c r="P166" s="40"/>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E167" s="3" t="s">
         <v>5</v>
       </c>
@@ -5456,7 +5488,7 @@
       <c r="O167" s="39"/>
       <c r="P167" s="40"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E168" s="3" t="s">
         <v>6</v>
       </c>
@@ -5482,7 +5514,7 @@
       <c r="O168" s="39"/>
       <c r="P168" s="40"/>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E169" s="3" t="s">
         <v>7</v>
       </c>
@@ -5508,7 +5540,7 @@
       <c r="O169" s="39"/>
       <c r="P169" s="40"/>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E170" s="3" t="s">
         <v>8</v>
       </c>
@@ -5534,7 +5566,7 @@
       <c r="O170" s="39"/>
       <c r="P170" s="40"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F172" s="5" t="s">
         <v>10</v>
       </c>
@@ -5542,13 +5574,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F173" s="31" t="s">
         <v>75</v>
       </c>
       <c r="G173" s="31"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F174" s="14">
         <v>320.70999999999998</v>
       </c>
@@ -5557,7 +5589,7 @@
         <v>47.56</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F175" s="14">
         <v>289.10000000000002</v>
       </c>
@@ -5566,7 +5598,7 @@
         <v>15.950000000000045</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F176" s="14">
         <v>285.43</v>
       </c>
@@ -5575,7 +5607,7 @@
         <v>12.28000000000003</v>
       </c>
     </row>
-    <row r="177" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F177" s="14">
         <v>350.92</v>
       </c>
@@ -5584,7 +5616,7 @@
         <v>77.770000000000039</v>
       </c>
     </row>
-    <row r="178" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F178" s="14">
         <v>246.53</v>
       </c>
@@ -5593,7 +5625,7 @@
         <v>-26.619999999999976</v>
       </c>
     </row>
-    <row r="179" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F179" s="14">
         <v>210.43</v>
       </c>
@@ -5602,7 +5634,7 @@
         <v>-62.71999999999997</v>
       </c>
     </row>
-    <row r="180" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F180" s="14">
         <v>246.53</v>
       </c>
@@ -5611,7 +5643,7 @@
         <v>-26.619999999999976</v>
       </c>
     </row>
-    <row r="181" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F181" s="16">
         <v>210.43</v>
       </c>
@@ -5620,7 +5652,7 @@
         <v>-62.71999999999997</v>
       </c>
     </row>
-    <row r="182" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F182" s="14">
         <v>283.31</v>
       </c>
@@ -5779,29 +5811,29 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A4:L172"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A4:L262"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="96.88671875" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="96.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E4" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E5" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E6" s="8" t="s">
         <v>113</v>
       </c>
@@ -5813,7 +5845,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E7" s="6" t="s">
         <v>116</v>
       </c>
@@ -5827,7 +5859,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
         <v>19</v>
       </c>
@@ -5854,7 +5886,7 @@
       </c>
       <c r="L8" s="38"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="35"/>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
@@ -5875,7 +5907,7 @@
       </c>
       <c r="L9" s="47"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="35"/>
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
@@ -5900,7 +5932,7 @@
       <c r="K10" s="46"/>
       <c r="L10" s="47"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="35"/>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
@@ -5925,7 +5957,7 @@
       <c r="K11" s="46"/>
       <c r="L11" s="47"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="35"/>
       <c r="B12" s="35"/>
       <c r="C12" s="35"/>
@@ -5950,7 +5982,7 @@
       <c r="K12" s="46"/>
       <c r="L12" s="47"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="35"/>
       <c r="B13" s="35"/>
       <c r="C13" s="35"/>
@@ -5975,7 +6007,7 @@
       <c r="K13" s="46"/>
       <c r="L13" s="47"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="35"/>
       <c r="B14" s="35"/>
       <c r="C14" s="35"/>
@@ -6000,7 +6032,7 @@
       <c r="K14" s="46"/>
       <c r="L14" s="47"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E15" s="3" t="s">
         <v>82</v>
       </c>
@@ -6022,7 +6054,7 @@
       <c r="K15" s="46"/>
       <c r="L15" s="47"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E16" s="3" t="s">
         <v>3</v>
       </c>
@@ -6044,7 +6076,7 @@
       <c r="K16" s="46"/>
       <c r="L16" s="47"/>
     </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E17" s="3" t="s">
         <v>103</v>
       </c>
@@ -6066,7 +6098,7 @@
       <c r="K17" s="46"/>
       <c r="L17" s="47"/>
     </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E18" s="3" t="s">
         <v>83</v>
       </c>
@@ -6088,7 +6120,7 @@
       <c r="K18" s="46"/>
       <c r="L18" s="47"/>
     </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E19" s="3" t="s">
         <v>84</v>
       </c>
@@ -6110,7 +6142,7 @@
       <c r="K19" s="46"/>
       <c r="L19" s="47"/>
     </row>
-    <row r="20" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E20" s="3" t="s">
         <v>85</v>
       </c>
@@ -6132,7 +6164,7 @@
       <c r="K20" s="46"/>
       <c r="L20" s="47"/>
     </row>
-    <row r="21" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E21" s="3" t="s">
         <v>86</v>
       </c>
@@ -6154,7 +6186,7 @@
       <c r="K21" s="46"/>
       <c r="L21" s="47"/>
     </row>
-    <row r="22" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E22" s="3" t="s">
         <v>104</v>
       </c>
@@ -6176,7 +6208,7 @@
       <c r="K22" s="46"/>
       <c r="L22" s="47"/>
     </row>
-    <row r="23" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E23" s="3" t="s">
         <v>105</v>
       </c>
@@ -6198,7 +6230,7 @@
       <c r="K23" s="46"/>
       <c r="L23" s="47"/>
     </row>
-    <row r="24" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
@@ -6220,7 +6252,7 @@
       <c r="K24" s="46"/>
       <c r="L24" s="47"/>
     </row>
-    <row r="25" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E25" s="3" t="s">
         <v>4</v>
       </c>
@@ -6242,7 +6274,7 @@
       <c r="K25" s="46"/>
       <c r="L25" s="47"/>
     </row>
-    <row r="26" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E26" s="3" t="s">
         <v>107</v>
       </c>
@@ -6264,7 +6296,7 @@
       <c r="K26" s="46"/>
       <c r="L26" s="47"/>
     </row>
-    <row r="27" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E27" s="3" t="s">
         <v>108</v>
       </c>
@@ -6286,7 +6318,7 @@
       <c r="K27" s="46"/>
       <c r="L27" s="47"/>
     </row>
-    <row r="28" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E28" s="3" t="s">
         <v>109</v>
       </c>
@@ -6308,7 +6340,7 @@
       <c r="K28" s="46"/>
       <c r="L28" s="47"/>
     </row>
-    <row r="29" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E29" s="3" t="s">
         <v>92</v>
       </c>
@@ -6330,17 +6362,17 @@
       <c r="K29" s="46"/>
       <c r="L29" s="47"/>
     </row>
-    <row r="32" spans="5:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="32" spans="5:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E32" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E33" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E34" s="8" t="s">
         <v>21</v>
       </c>
@@ -6352,7 +6384,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E35" s="6" t="s">
         <v>116</v>
       </c>
@@ -6366,7 +6398,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="35" t="s">
         <v>16</v>
       </c>
@@ -6393,7 +6425,7 @@
       </c>
       <c r="L36" s="38"/>
     </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="35"/>
       <c r="B37" s="35"/>
       <c r="C37" s="35"/>
@@ -6414,7 +6446,7 @@
       </c>
       <c r="L37" s="47"/>
     </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="35"/>
       <c r="B38" s="35"/>
       <c r="C38" s="35"/>
@@ -6439,7 +6471,7 @@
       <c r="K38" s="46"/>
       <c r="L38" s="47"/>
     </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="35"/>
       <c r="B39" s="35"/>
       <c r="C39" s="35"/>
@@ -6464,7 +6496,7 @@
       <c r="K39" s="46"/>
       <c r="L39" s="47"/>
     </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" s="35"/>
       <c r="C40" s="35"/>
@@ -6489,7 +6521,7 @@
       <c r="K40" s="46"/>
       <c r="L40" s="47"/>
     </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="35"/>
       <c r="B41" s="35"/>
       <c r="C41" s="35"/>
@@ -6514,7 +6546,7 @@
       <c r="K41" s="46"/>
       <c r="L41" s="47"/>
     </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35"/>
@@ -6539,7 +6571,7 @@
       <c r="K42" s="46"/>
       <c r="L42" s="47"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E43" s="3" t="s">
         <v>82</v>
       </c>
@@ -6561,7 +6593,7 @@
       <c r="K43" s="46"/>
       <c r="L43" s="47"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
@@ -6583,7 +6615,7 @@
       <c r="K44" s="46"/>
       <c r="L44" s="47"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E45" s="3" t="s">
         <v>103</v>
       </c>
@@ -6605,7 +6637,7 @@
       <c r="K45" s="46"/>
       <c r="L45" s="47"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E46" s="3" t="s">
         <v>83</v>
       </c>
@@ -6627,7 +6659,7 @@
       <c r="K46" s="46"/>
       <c r="L46" s="47"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E47" s="3" t="s">
         <v>84</v>
       </c>
@@ -6649,7 +6681,7 @@
       <c r="K47" s="46"/>
       <c r="L47" s="47"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E48" s="3" t="s">
         <v>85</v>
       </c>
@@ -6671,7 +6703,7 @@
       <c r="K48" s="46"/>
       <c r="L48" s="47"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E49" s="3" t="s">
         <v>86</v>
       </c>
@@ -6693,7 +6725,7 @@
       <c r="K49" s="46"/>
       <c r="L49" s="47"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E50" s="3" t="s">
         <v>104</v>
       </c>
@@ -6715,7 +6747,7 @@
       <c r="K50" s="46"/>
       <c r="L50" s="47"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E51" s="3" t="s">
         <v>105</v>
       </c>
@@ -6737,7 +6769,7 @@
       <c r="K51" s="46"/>
       <c r="L51" s="47"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E52" s="3" t="s">
         <v>106</v>
       </c>
@@ -6759,7 +6791,7 @@
       <c r="K52" s="46"/>
       <c r="L52" s="47"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E53" s="3" t="s">
         <v>4</v>
       </c>
@@ -6781,7 +6813,7 @@
       <c r="K53" s="46"/>
       <c r="L53" s="47"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E54" s="3" t="s">
         <v>107</v>
       </c>
@@ -6803,7 +6835,7 @@
       <c r="K54" s="46"/>
       <c r="L54" s="47"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E55" s="3" t="s">
         <v>108</v>
       </c>
@@ -6825,7 +6857,7 @@
       <c r="K55" s="46"/>
       <c r="L55" s="47"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E56" s="3" t="s">
         <v>109</v>
       </c>
@@ -6847,7 +6879,7 @@
       <c r="K56" s="46"/>
       <c r="L56" s="47"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E57" s="3" t="s">
         <v>92</v>
       </c>
@@ -6869,17 +6901,17 @@
       <c r="K57" s="46"/>
       <c r="L57" s="47"/>
     </row>
-    <row r="60" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E60" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E61" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E62" s="8" t="s">
         <v>21</v>
       </c>
@@ -6891,7 +6923,7 @@
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
     </row>
-    <row r="63" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E63" s="6" t="s">
         <v>116</v>
       </c>
@@ -6905,7 +6937,7 @@
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="35" t="s">
         <v>23</v>
       </c>
@@ -6932,7 +6964,7 @@
       </c>
       <c r="L64" s="38"/>
     </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="35"/>
       <c r="B65" s="35"/>
       <c r="C65" s="35"/>
@@ -6953,7 +6985,7 @@
       </c>
       <c r="L65" s="47"/>
     </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="35"/>
       <c r="B66" s="35"/>
       <c r="C66" s="35"/>
@@ -6978,7 +7010,7 @@
       <c r="K66" s="46"/>
       <c r="L66" s="47"/>
     </row>
-    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="35"/>
@@ -7003,7 +7035,7 @@
       <c r="K67" s="46"/>
       <c r="L67" s="47"/>
     </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
@@ -7028,7 +7060,7 @@
       <c r="K68" s="46"/>
       <c r="L68" s="47"/>
     </row>
-    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="35"/>
       <c r="B69" s="35"/>
       <c r="C69" s="35"/>
@@ -7053,7 +7085,7 @@
       <c r="K69" s="46"/>
       <c r="L69" s="47"/>
     </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="35"/>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
@@ -7078,7 +7110,7 @@
       <c r="K70" s="46"/>
       <c r="L70" s="47"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E71" s="3" t="s">
         <v>82</v>
       </c>
@@ -7100,7 +7132,7 @@
       <c r="K71" s="46"/>
       <c r="L71" s="47"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7122,7 +7154,7 @@
       <c r="K72" s="46"/>
       <c r="L72" s="47"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E73" s="3" t="s">
         <v>103</v>
       </c>
@@ -7144,7 +7176,7 @@
       <c r="K73" s="46"/>
       <c r="L73" s="47"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E74" s="3" t="s">
         <v>83</v>
       </c>
@@ -7166,7 +7198,7 @@
       <c r="K74" s="46"/>
       <c r="L74" s="47"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E75" s="3" t="s">
         <v>84</v>
       </c>
@@ -7188,7 +7220,7 @@
       <c r="K75" s="46"/>
       <c r="L75" s="47"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E76" s="3" t="s">
         <v>85</v>
       </c>
@@ -7210,7 +7242,7 @@
       <c r="K76" s="46"/>
       <c r="L76" s="47"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E77" s="3" t="s">
         <v>86</v>
       </c>
@@ -7232,7 +7264,7 @@
       <c r="K77" s="46"/>
       <c r="L77" s="47"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E78" s="3" t="s">
         <v>104</v>
       </c>
@@ -7254,7 +7286,7 @@
       <c r="K78" s="46"/>
       <c r="L78" s="47"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E79" s="3" t="s">
         <v>105</v>
       </c>
@@ -7276,7 +7308,7 @@
       <c r="K79" s="46"/>
       <c r="L79" s="47"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E80" s="3" t="s">
         <v>106</v>
       </c>
@@ -7298,7 +7330,7 @@
       <c r="K80" s="46"/>
       <c r="L80" s="47"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E81" s="3" t="s">
         <v>4</v>
       </c>
@@ -7320,7 +7352,7 @@
       <c r="K81" s="46"/>
       <c r="L81" s="47"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E82" s="3" t="s">
         <v>107</v>
       </c>
@@ -7342,7 +7374,7 @@
       <c r="K82" s="46"/>
       <c r="L82" s="47"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E83" s="3" t="s">
         <v>108</v>
       </c>
@@ -7364,7 +7396,7 @@
       <c r="K83" s="46"/>
       <c r="L83" s="47"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E84" s="3" t="s">
         <v>109</v>
       </c>
@@ -7386,7 +7418,7 @@
       <c r="K84" s="46"/>
       <c r="L84" s="47"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E85" s="3" t="s">
         <v>92</v>
       </c>
@@ -7408,22 +7440,22 @@
       <c r="K85" s="46"/>
       <c r="L85" s="47"/>
     </row>
-    <row r="88" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E88" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E89" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E90" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E91" s="8" t="s">
         <v>21</v>
       </c>
@@ -7435,7 +7467,7 @@
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
     </row>
-    <row r="92" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E92" s="6" t="s">
         <v>116</v>
       </c>
@@ -7449,7 +7481,7 @@
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
     </row>
-    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="35" t="s">
         <v>123</v>
       </c>
@@ -7476,7 +7508,7 @@
       </c>
       <c r="L93" s="38"/>
     </row>
-    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="35"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35"/>
@@ -7497,7 +7529,7 @@
       </c>
       <c r="L94" s="47"/>
     </row>
-    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="35"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35"/>
@@ -7522,7 +7554,7 @@
       <c r="K95" s="46"/>
       <c r="L95" s="47"/>
     </row>
-    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="35"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35"/>
@@ -7547,7 +7579,7 @@
       <c r="K96" s="46"/>
       <c r="L96" s="47"/>
     </row>
-    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="35"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35"/>
@@ -7572,7 +7604,7 @@
       <c r="K97" s="46"/>
       <c r="L97" s="47"/>
     </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="35"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35"/>
@@ -7597,7 +7629,7 @@
       <c r="K98" s="46"/>
       <c r="L98" s="47"/>
     </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="35"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35"/>
@@ -7622,7 +7654,7 @@
       <c r="K99" s="46"/>
       <c r="L99" s="47"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E100" s="3" t="s">
         <v>82</v>
       </c>
@@ -7644,7 +7676,7 @@
       <c r="K100" s="46"/>
       <c r="L100" s="47"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7666,7 +7698,7 @@
       <c r="K101" s="46"/>
       <c r="L101" s="47"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E102" s="3" t="s">
         <v>103</v>
       </c>
@@ -7688,7 +7720,7 @@
       <c r="K102" s="46"/>
       <c r="L102" s="47"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E103" s="3" t="s">
         <v>83</v>
       </c>
@@ -7710,7 +7742,7 @@
       <c r="K103" s="46"/>
       <c r="L103" s="47"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E104" s="3" t="s">
         <v>84</v>
       </c>
@@ -7732,7 +7764,7 @@
       <c r="K104" s="46"/>
       <c r="L104" s="47"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E105" s="3" t="s">
         <v>85</v>
       </c>
@@ -7754,7 +7786,7 @@
       <c r="K105" s="46"/>
       <c r="L105" s="47"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E106" s="3" t="s">
         <v>86</v>
       </c>
@@ -7776,7 +7808,7 @@
       <c r="K106" s="46"/>
       <c r="L106" s="47"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E107" s="3" t="s">
         <v>104</v>
       </c>
@@ -7798,7 +7830,7 @@
       <c r="K107" s="46"/>
       <c r="L107" s="47"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E108" s="3" t="s">
         <v>105</v>
       </c>
@@ -7820,7 +7852,7 @@
       <c r="K108" s="46"/>
       <c r="L108" s="47"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E109" s="3" t="s">
         <v>106</v>
       </c>
@@ -7842,7 +7874,7 @@
       <c r="K109" s="46"/>
       <c r="L109" s="47"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E110" s="3" t="s">
         <v>4</v>
       </c>
@@ -7864,7 +7896,7 @@
       <c r="K110" s="46"/>
       <c r="L110" s="47"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E111" s="3" t="s">
         <v>107</v>
       </c>
@@ -7886,7 +7918,7 @@
       <c r="K111" s="46"/>
       <c r="L111" s="47"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E112" s="3" t="s">
         <v>108</v>
       </c>
@@ -7908,7 +7940,7 @@
       <c r="K112" s="46"/>
       <c r="L112" s="47"/>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E113" s="3" t="s">
         <v>109</v>
       </c>
@@ -7930,7 +7962,7 @@
       <c r="K113" s="46"/>
       <c r="L113" s="47"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E114" s="3" t="s">
         <v>92</v>
       </c>
@@ -7952,22 +7984,22 @@
       <c r="K114" s="46"/>
       <c r="L114" s="47"/>
     </row>
-    <row r="117" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E117" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E118" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E119" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E120" s="8" t="s">
         <v>128</v>
       </c>
@@ -7979,7 +8011,7 @@
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
     </row>
-    <row r="121" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E121" s="6" t="s">
         <v>116</v>
       </c>
@@ -7993,7 +8025,7 @@
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="35" t="s">
         <v>126</v>
       </c>
@@ -8020,7 +8052,7 @@
       </c>
       <c r="L122" s="38"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="35"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35"/>
@@ -8041,7 +8073,7 @@
       </c>
       <c r="L123" s="47"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="35"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35"/>
@@ -8066,7 +8098,7 @@
       <c r="K124" s="46"/>
       <c r="L124" s="47"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="35"/>
       <c r="B125" s="35"/>
       <c r="C125" s="35"/>
@@ -8091,7 +8123,7 @@
       <c r="K125" s="46"/>
       <c r="L125" s="47"/>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="35"/>
       <c r="B126" s="35"/>
       <c r="C126" s="35"/>
@@ -8116,7 +8148,7 @@
       <c r="K126" s="46"/>
       <c r="L126" s="47"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="35"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35"/>
@@ -8141,7 +8173,7 @@
       <c r="K127" s="46"/>
       <c r="L127" s="47"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="35"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
@@ -8166,7 +8198,7 @@
       <c r="K128" s="46"/>
       <c r="L128" s="47"/>
     </row>
-    <row r="129" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E129" s="3" t="s">
         <v>82</v>
       </c>
@@ -8188,7 +8220,7 @@
       <c r="K129" s="46"/>
       <c r="L129" s="47"/>
     </row>
-    <row r="130" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E130" s="3" t="s">
         <v>3</v>
       </c>
@@ -8210,7 +8242,7 @@
       <c r="K130" s="46"/>
       <c r="L130" s="47"/>
     </row>
-    <row r="131" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E131" s="3" t="s">
         <v>103</v>
       </c>
@@ -8232,7 +8264,7 @@
       <c r="K131" s="46"/>
       <c r="L131" s="47"/>
     </row>
-    <row r="132" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E132" s="3" t="s">
         <v>83</v>
       </c>
@@ -8254,7 +8286,7 @@
       <c r="K132" s="46"/>
       <c r="L132" s="47"/>
     </row>
-    <row r="133" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E133" s="3" t="s">
         <v>84</v>
       </c>
@@ -8276,7 +8308,7 @@
       <c r="K133" s="46"/>
       <c r="L133" s="47"/>
     </row>
-    <row r="134" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E134" s="3" t="s">
         <v>85</v>
       </c>
@@ -8298,7 +8330,7 @@
       <c r="K134" s="46"/>
       <c r="L134" s="47"/>
     </row>
-    <row r="135" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E135" s="3" t="s">
         <v>86</v>
       </c>
@@ -8320,7 +8352,7 @@
       <c r="K135" s="46"/>
       <c r="L135" s="47"/>
     </row>
-    <row r="136" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E136" s="3" t="s">
         <v>104</v>
       </c>
@@ -8342,7 +8374,7 @@
       <c r="K136" s="46"/>
       <c r="L136" s="47"/>
     </row>
-    <row r="137" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E137" s="3" t="s">
         <v>105</v>
       </c>
@@ -8364,7 +8396,7 @@
       <c r="K137" s="46"/>
       <c r="L137" s="47"/>
     </row>
-    <row r="138" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E138" s="3" t="s">
         <v>106</v>
       </c>
@@ -8386,7 +8418,7 @@
       <c r="K138" s="46"/>
       <c r="L138" s="47"/>
     </row>
-    <row r="139" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E139" s="3" t="s">
         <v>4</v>
       </c>
@@ -8408,7 +8440,7 @@
       <c r="K139" s="46"/>
       <c r="L139" s="47"/>
     </row>
-    <row r="140" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E140" s="3" t="s">
         <v>107</v>
       </c>
@@ -8430,7 +8462,7 @@
       <c r="K140" s="46"/>
       <c r="L140" s="47"/>
     </row>
-    <row r="141" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E141" s="3" t="s">
         <v>108</v>
       </c>
@@ -8452,7 +8484,7 @@
       <c r="K141" s="46"/>
       <c r="L141" s="47"/>
     </row>
-    <row r="142" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E142" s="3" t="s">
         <v>109</v>
       </c>
@@ -8474,7 +8506,7 @@
       <c r="K142" s="46"/>
       <c r="L142" s="47"/>
     </row>
-    <row r="143" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E143" s="3" t="s">
         <v>92</v>
       </c>
@@ -8496,22 +8528,22 @@
       <c r="K143" s="46"/>
       <c r="L143" s="47"/>
     </row>
-    <row r="146" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E146" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E147" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E148" s="8" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E149" s="8" t="s">
         <v>21</v>
       </c>
@@ -8523,7 +8555,7 @@
       <c r="K149" s="1"/>
       <c r="L149" s="1"/>
     </row>
-    <row r="150" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="E150" s="6" t="s">
         <v>116</v>
       </c>
@@ -8537,9 +8569,9 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B151" s="35"/>
       <c r="C151" s="35"/>
@@ -8564,7 +8596,7 @@
       </c>
       <c r="L151" s="38"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="35"/>
       <c r="B152" s="35"/>
       <c r="C152" s="35"/>
@@ -8581,11 +8613,11 @@
       </c>
       <c r="J152" s="31"/>
       <c r="K152" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L152" s="47"/>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="35"/>
       <c r="B153" s="35"/>
       <c r="C153" s="35"/>
@@ -8610,7 +8642,7 @@
       <c r="K153" s="46"/>
       <c r="L153" s="47"/>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="35"/>
       <c r="B154" s="35"/>
       <c r="C154" s="35"/>
@@ -8635,7 +8667,7 @@
       <c r="K154" s="46"/>
       <c r="L154" s="47"/>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="35"/>
       <c r="B155" s="35"/>
       <c r="C155" s="35"/>
@@ -8660,7 +8692,7 @@
       <c r="K155" s="46"/>
       <c r="L155" s="47"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="35"/>
       <c r="B156" s="35"/>
       <c r="C156" s="35"/>
@@ -8685,7 +8717,7 @@
       <c r="K156" s="46"/>
       <c r="L156" s="47"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="35"/>
       <c r="B157" s="35"/>
       <c r="C157" s="35"/>
@@ -8710,7 +8742,7 @@
       <c r="K157" s="46"/>
       <c r="L157" s="47"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E158" s="3" t="s">
         <v>82</v>
       </c>
@@ -8732,7 +8764,7 @@
       <c r="K158" s="46"/>
       <c r="L158" s="47"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E159" s="3" t="s">
         <v>3</v>
       </c>
@@ -8754,7 +8786,7 @@
       <c r="K159" s="46"/>
       <c r="L159" s="47"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E160" s="3" t="s">
         <v>103</v>
       </c>
@@ -8776,7 +8808,7 @@
       <c r="K160" s="46"/>
       <c r="L160" s="47"/>
     </row>
-    <row r="161" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E161" s="3" t="s">
         <v>83</v>
       </c>
@@ -8798,7 +8830,7 @@
       <c r="K161" s="46"/>
       <c r="L161" s="47"/>
     </row>
-    <row r="162" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E162" s="3" t="s">
         <v>84</v>
       </c>
@@ -8820,7 +8852,7 @@
       <c r="K162" s="46"/>
       <c r="L162" s="47"/>
     </row>
-    <row r="163" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E163" s="3" t="s">
         <v>85</v>
       </c>
@@ -8842,7 +8874,7 @@
       <c r="K163" s="46"/>
       <c r="L163" s="47"/>
     </row>
-    <row r="164" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E164" s="3" t="s">
         <v>86</v>
       </c>
@@ -8864,7 +8896,7 @@
       <c r="K164" s="46"/>
       <c r="L164" s="47"/>
     </row>
-    <row r="165" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E165" s="3" t="s">
         <v>104</v>
       </c>
@@ -8886,7 +8918,7 @@
       <c r="K165" s="46"/>
       <c r="L165" s="47"/>
     </row>
-    <row r="166" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E166" s="3" t="s">
         <v>105</v>
       </c>
@@ -8908,7 +8940,7 @@
       <c r="K166" s="46"/>
       <c r="L166" s="47"/>
     </row>
-    <row r="167" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E167" s="3" t="s">
         <v>106</v>
       </c>
@@ -8930,7 +8962,7 @@
       <c r="K167" s="46"/>
       <c r="L167" s="47"/>
     </row>
-    <row r="168" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E168" s="3" t="s">
         <v>4</v>
       </c>
@@ -8952,7 +8984,7 @@
       <c r="K168" s="46"/>
       <c r="L168" s="47"/>
     </row>
-    <row r="169" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E169" s="3" t="s">
         <v>107</v>
       </c>
@@ -8974,7 +9006,7 @@
       <c r="K169" s="46"/>
       <c r="L169" s="47"/>
     </row>
-    <row r="170" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E170" s="3" t="s">
         <v>108</v>
       </c>
@@ -8996,7 +9028,7 @@
       <c r="K170" s="46"/>
       <c r="L170" s="47"/>
     </row>
-    <row r="171" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E171" s="3" t="s">
         <v>109</v>
       </c>
@@ -9018,7 +9050,7 @@
       <c r="K171" s="46"/>
       <c r="L171" s="47"/>
     </row>
-    <row r="172" spans="5:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="5:12" x14ac:dyDescent="0.25">
       <c r="E172" s="3" t="s">
         <v>92</v>
       </c>
@@ -9040,8 +9072,1657 @@
       <c r="K172" s="46"/>
       <c r="L172" s="47"/>
     </row>
+    <row r="175" spans="5:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E175" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="176" spans="5:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E176" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E177" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E178" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F178" s="1"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+      <c r="J178" s="1"/>
+      <c r="K178" s="1"/>
+      <c r="L178" s="1"/>
+    </row>
+    <row r="179" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E179" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F179" s="1"/>
+      <c r="G179" s="1"/>
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+      <c r="J179" s="1"/>
+      <c r="K179" s="1"/>
+      <c r="L179" s="1"/>
+    </row>
+    <row r="180" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E180" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F180" s="10"/>
+      <c r="G180" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="H180" s="42"/>
+      <c r="I180" s="42"/>
+      <c r="J180" s="42"/>
+      <c r="K180" s="1"/>
+      <c r="L180" s="1"/>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="B181" s="35"/>
+      <c r="C181" s="35"/>
+      <c r="E181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="43"/>
+      <c r="G181" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I181" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J181" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K181" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L181" s="38"/>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" s="35"/>
+      <c r="B182" s="35"/>
+      <c r="C182" s="35"/>
+      <c r="E182" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F182" s="44"/>
+      <c r="G182" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H182" s="31"/>
+      <c r="I182" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="J182" s="31"/>
+      <c r="K182" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="L182" s="47"/>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" s="35"/>
+      <c r="B183" s="35"/>
+      <c r="C183" s="35"/>
+      <c r="E183" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F183" s="44"/>
+      <c r="G183" s="28">
+        <v>286.27</v>
+      </c>
+      <c r="H183" s="29">
+        <f>G183-273.15</f>
+        <v>13.120000000000005</v>
+      </c>
+      <c r="I183" s="28">
+        <v>247.98</v>
+      </c>
+      <c r="J183" s="29">
+        <f>I183-273.15</f>
+        <v>-25.169999999999987</v>
+      </c>
+      <c r="K183" s="46"/>
+      <c r="L183" s="47"/>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" s="35"/>
+      <c r="B184" s="35"/>
+      <c r="C184" s="35"/>
+      <c r="E184" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F184" s="44"/>
+      <c r="G184" s="28">
+        <v>286.29000000000002</v>
+      </c>
+      <c r="H184" s="29">
+        <f t="shared" ref="H184:H202" si="12">G184-273.15</f>
+        <v>13.140000000000043</v>
+      </c>
+      <c r="I184" s="28">
+        <v>247.99</v>
+      </c>
+      <c r="J184" s="29">
+        <f t="shared" ref="J184:J202" si="13">I184-273.15</f>
+        <v>-25.159999999999968</v>
+      </c>
+      <c r="K184" s="46"/>
+      <c r="L184" s="47"/>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" s="35"/>
+      <c r="B185" s="35"/>
+      <c r="C185" s="35"/>
+      <c r="E185" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F185" s="44"/>
+      <c r="G185" s="28">
+        <v>286.14999999999998</v>
+      </c>
+      <c r="H185" s="29">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="I185" s="28">
+        <v>247.87</v>
+      </c>
+      <c r="J185" s="29">
+        <f t="shared" si="13"/>
+        <v>-25.279999999999973</v>
+      </c>
+      <c r="K185" s="46"/>
+      <c r="L185" s="47"/>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" s="35"/>
+      <c r="B186" s="35"/>
+      <c r="C186" s="35"/>
+      <c r="E186" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F186" s="44"/>
+      <c r="G186" s="28">
+        <v>286.17</v>
+      </c>
+      <c r="H186" s="29">
+        <f t="shared" si="12"/>
+        <v>13.020000000000039</v>
+      </c>
+      <c r="I186" s="28">
+        <v>247.88</v>
+      </c>
+      <c r="J186" s="29">
+        <f t="shared" si="13"/>
+        <v>-25.269999999999982</v>
+      </c>
+      <c r="K186" s="46"/>
+      <c r="L186" s="47"/>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" s="35"/>
+      <c r="B187" s="35"/>
+      <c r="C187" s="35"/>
+      <c r="E187" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F187" s="44"/>
+      <c r="G187" s="28">
+        <v>286.14999999999998</v>
+      </c>
+      <c r="H187" s="29">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="I187" s="28">
+        <v>247.87</v>
+      </c>
+      <c r="J187" s="29">
+        <f t="shared" si="13"/>
+        <v>-25.279999999999973</v>
+      </c>
+      <c r="K187" s="46"/>
+      <c r="L187" s="47"/>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E188" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F188" s="44"/>
+      <c r="G188" s="28">
+        <v>286.17</v>
+      </c>
+      <c r="H188" s="29">
+        <f t="shared" si="12"/>
+        <v>13.020000000000039</v>
+      </c>
+      <c r="I188" s="28">
+        <v>247.88</v>
+      </c>
+      <c r="J188" s="29">
+        <f t="shared" si="13"/>
+        <v>-25.269999999999982</v>
+      </c>
+      <c r="K188" s="46"/>
+      <c r="L188" s="47"/>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E189" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F189" s="44"/>
+      <c r="G189" s="28">
+        <v>368.8</v>
+      </c>
+      <c r="H189" s="29">
+        <f t="shared" si="12"/>
+        <v>95.650000000000034</v>
+      </c>
+      <c r="I189" s="28">
+        <v>348.4</v>
+      </c>
+      <c r="J189" s="29">
+        <f t="shared" si="13"/>
+        <v>75.25</v>
+      </c>
+      <c r="K189" s="46"/>
+      <c r="L189" s="47"/>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E190" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F190" s="44"/>
+      <c r="G190" s="28">
+        <v>362.96</v>
+      </c>
+      <c r="H190" s="29">
+        <f t="shared" si="12"/>
+        <v>89.81</v>
+      </c>
+      <c r="I190" s="28">
+        <v>342.4</v>
+      </c>
+      <c r="J190" s="29">
+        <f t="shared" si="13"/>
+        <v>69.25</v>
+      </c>
+      <c r="K190" s="46"/>
+      <c r="L190" s="47"/>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E191" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F191" s="44"/>
+      <c r="G191" s="28">
+        <v>284</v>
+      </c>
+      <c r="H191" s="29">
+        <f t="shared" si="12"/>
+        <v>10.850000000000023</v>
+      </c>
+      <c r="I191" s="28">
+        <v>244.25</v>
+      </c>
+      <c r="J191" s="29">
+        <f t="shared" si="13"/>
+        <v>-28.899999999999977</v>
+      </c>
+      <c r="K191" s="46"/>
+      <c r="L191" s="47"/>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E192" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F192" s="44"/>
+      <c r="G192" s="30">
+        <v>282.86</v>
+      </c>
+      <c r="H192" s="29">
+        <f t="shared" si="12"/>
+        <v>9.7100000000000364</v>
+      </c>
+      <c r="I192" s="28">
+        <v>242.93</v>
+      </c>
+      <c r="J192" s="29">
+        <f t="shared" si="13"/>
+        <v>-30.21999999999997</v>
+      </c>
+      <c r="K192" s="46"/>
+      <c r="L192" s="47"/>
+    </row>
+    <row r="193" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E193" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F193" s="44"/>
+      <c r="G193" s="30">
+        <v>282.83999999999997</v>
+      </c>
+      <c r="H193" s="29">
+        <f t="shared" si="12"/>
+        <v>9.6899999999999977</v>
+      </c>
+      <c r="I193" s="28">
+        <v>242.92</v>
+      </c>
+      <c r="J193" s="29">
+        <f t="shared" si="13"/>
+        <v>-30.22999999999999</v>
+      </c>
+      <c r="K193" s="46"/>
+      <c r="L193" s="47"/>
+    </row>
+    <row r="194" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E194" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F194" s="44"/>
+      <c r="G194" s="28">
+        <v>282.83</v>
+      </c>
+      <c r="H194" s="29">
+        <f t="shared" si="12"/>
+        <v>9.6800000000000068</v>
+      </c>
+      <c r="I194" s="28">
+        <v>242.91</v>
+      </c>
+      <c r="J194" s="29">
+        <f t="shared" si="13"/>
+        <v>-30.239999999999981</v>
+      </c>
+      <c r="K194" s="46"/>
+      <c r="L194" s="47"/>
+    </row>
+    <row r="195" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E195" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F195" s="44"/>
+      <c r="G195" s="28">
+        <v>286.12</v>
+      </c>
+      <c r="H195" s="29">
+        <f t="shared" si="12"/>
+        <v>12.970000000000027</v>
+      </c>
+      <c r="I195" s="28">
+        <v>247.84</v>
+      </c>
+      <c r="J195" s="29">
+        <f t="shared" si="13"/>
+        <v>-25.309999999999974</v>
+      </c>
+      <c r="K195" s="46"/>
+      <c r="L195" s="47"/>
+    </row>
+    <row r="196" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E196" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F196" s="44"/>
+      <c r="G196" s="28">
+        <v>286.2</v>
+      </c>
+      <c r="H196" s="29">
+        <f t="shared" si="12"/>
+        <v>13.050000000000011</v>
+      </c>
+      <c r="I196" s="28">
+        <v>247.91</v>
+      </c>
+      <c r="J196" s="29">
+        <f t="shared" si="13"/>
+        <v>-25.239999999999981</v>
+      </c>
+      <c r="K196" s="46"/>
+      <c r="L196" s="47"/>
+    </row>
+    <row r="197" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E197" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F197" s="44"/>
+      <c r="G197" s="28">
+        <v>286.14999999999998</v>
+      </c>
+      <c r="H197" s="29">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="I197" s="28">
+        <v>247.86</v>
+      </c>
+      <c r="J197" s="29">
+        <f t="shared" si="13"/>
+        <v>-25.289999999999964</v>
+      </c>
+      <c r="K197" s="46"/>
+      <c r="L197" s="47"/>
+    </row>
+    <row r="198" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E198" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F198" s="44"/>
+      <c r="G198" s="28">
+        <v>282.44</v>
+      </c>
+      <c r="H198" s="29">
+        <f t="shared" si="12"/>
+        <v>9.2900000000000205</v>
+      </c>
+      <c r="I198" s="28">
+        <v>242.52</v>
+      </c>
+      <c r="J198" s="29">
+        <f t="shared" si="13"/>
+        <v>-30.629999999999967</v>
+      </c>
+      <c r="K198" s="46"/>
+      <c r="L198" s="47"/>
+    </row>
+    <row r="199" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E199" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F199" s="44"/>
+      <c r="G199" s="28">
+        <v>282.41000000000003</v>
+      </c>
+      <c r="H199" s="29">
+        <f t="shared" si="12"/>
+        <v>9.2600000000000477</v>
+      </c>
+      <c r="I199" s="28">
+        <v>242.5</v>
+      </c>
+      <c r="J199" s="29">
+        <f t="shared" si="13"/>
+        <v>-30.649999999999977</v>
+      </c>
+      <c r="K199" s="46"/>
+      <c r="L199" s="47"/>
+    </row>
+    <row r="200" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E200" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F200" s="44"/>
+      <c r="G200" s="28">
+        <v>283.14999999999998</v>
+      </c>
+      <c r="H200" s="29">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="I200" s="28">
+        <v>243.21</v>
+      </c>
+      <c r="J200" s="29">
+        <f t="shared" si="13"/>
+        <v>-29.939999999999969</v>
+      </c>
+      <c r="K200" s="46"/>
+      <c r="L200" s="47"/>
+    </row>
+    <row r="201" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E201" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F201" s="44"/>
+      <c r="G201" s="28">
+        <v>283.13</v>
+      </c>
+      <c r="H201" s="29">
+        <f t="shared" si="12"/>
+        <v>9.9800000000000182</v>
+      </c>
+      <c r="I201" s="28">
+        <v>243.18</v>
+      </c>
+      <c r="J201" s="29">
+        <f t="shared" si="13"/>
+        <v>-29.96999999999997</v>
+      </c>
+      <c r="K201" s="46"/>
+      <c r="L201" s="47"/>
+    </row>
+    <row r="202" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E202" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F202" s="45"/>
+      <c r="G202" s="28">
+        <v>288.75</v>
+      </c>
+      <c r="H202" s="29">
+        <f t="shared" si="12"/>
+        <v>15.600000000000023</v>
+      </c>
+      <c r="I202" s="28">
+        <v>250.75</v>
+      </c>
+      <c r="J202" s="29">
+        <f t="shared" si="13"/>
+        <v>-22.399999999999977</v>
+      </c>
+      <c r="K202" s="46"/>
+      <c r="L202" s="47"/>
+    </row>
+    <row r="205" spans="5:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E205" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="206" spans="5:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E206" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="207" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E207" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="208" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E208" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F208" s="1"/>
+      <c r="G208" s="1"/>
+      <c r="H208" s="1"/>
+      <c r="I208" s="1"/>
+      <c r="J208" s="1"/>
+      <c r="K208" s="1"/>
+      <c r="L208" s="1"/>
+    </row>
+    <row r="209" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E209" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F209" s="1"/>
+      <c r="G209" s="1"/>
+      <c r="H209" s="1"/>
+      <c r="I209" s="1"/>
+      <c r="J209" s="1"/>
+      <c r="K209" s="1"/>
+      <c r="L209" s="1"/>
+    </row>
+    <row r="210" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E210" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F210" s="10"/>
+      <c r="G210" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="H210" s="42"/>
+      <c r="I210" s="42"/>
+      <c r="J210" s="42"/>
+      <c r="K210" s="1"/>
+      <c r="L210" s="1"/>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B211" s="35"/>
+      <c r="C211" s="35"/>
+      <c r="E211" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F211" s="43"/>
+      <c r="G211" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H211" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I211" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J211" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K211" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L211" s="38"/>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" s="35"/>
+      <c r="B212" s="35"/>
+      <c r="C212" s="35"/>
+      <c r="E212" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F212" s="44"/>
+      <c r="G212" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H212" s="31"/>
+      <c r="I212" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="J212" s="31"/>
+      <c r="K212" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="L212" s="47"/>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" s="35"/>
+      <c r="B213" s="35"/>
+      <c r="C213" s="35"/>
+      <c r="E213" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F213" s="44"/>
+      <c r="G213" s="28">
+        <v>266.52999999999997</v>
+      </c>
+      <c r="H213" s="29">
+        <f>G213-273.15</f>
+        <v>-6.6200000000000045</v>
+      </c>
+      <c r="I213" s="28">
+        <v>254.91</v>
+      </c>
+      <c r="J213" s="29">
+        <f>I213-273.15</f>
+        <v>-18.239999999999981</v>
+      </c>
+      <c r="K213" s="46"/>
+      <c r="L213" s="47"/>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A214" s="35"/>
+      <c r="B214" s="35"/>
+      <c r="C214" s="35"/>
+      <c r="E214" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F214" s="44"/>
+      <c r="G214" s="28">
+        <v>266.54000000000002</v>
+      </c>
+      <c r="H214" s="29">
+        <f t="shared" ref="H214:H232" si="14">G214-273.15</f>
+        <v>-6.6099999999999568</v>
+      </c>
+      <c r="I214" s="28">
+        <v>254.92</v>
+      </c>
+      <c r="J214" s="29">
+        <f t="shared" ref="J214:J232" si="15">I214-273.15</f>
+        <v>-18.22999999999999</v>
+      </c>
+      <c r="K214" s="46"/>
+      <c r="L214" s="47"/>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A215" s="35"/>
+      <c r="B215" s="35"/>
+      <c r="C215" s="35"/>
+      <c r="E215" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F215" s="44"/>
+      <c r="G215" s="28">
+        <v>266.45</v>
+      </c>
+      <c r="H215" s="29">
+        <f t="shared" si="14"/>
+        <v>-6.6999999999999886</v>
+      </c>
+      <c r="I215" s="28">
+        <v>254.83</v>
+      </c>
+      <c r="J215" s="29">
+        <f t="shared" si="15"/>
+        <v>-18.319999999999965</v>
+      </c>
+      <c r="K215" s="46"/>
+      <c r="L215" s="47"/>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" s="35"/>
+      <c r="B216" s="35"/>
+      <c r="C216" s="35"/>
+      <c r="E216" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F216" s="44"/>
+      <c r="G216" s="28">
+        <v>266.45999999999998</v>
+      </c>
+      <c r="H216" s="29">
+        <f t="shared" si="14"/>
+        <v>-6.6899999999999977</v>
+      </c>
+      <c r="I216" s="28">
+        <v>254.84</v>
+      </c>
+      <c r="J216" s="29">
+        <f t="shared" si="15"/>
+        <v>-18.309999999999974</v>
+      </c>
+      <c r="K216" s="46"/>
+      <c r="L216" s="47"/>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" s="35"/>
+      <c r="B217" s="35"/>
+      <c r="C217" s="35"/>
+      <c r="E217" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F217" s="44"/>
+      <c r="G217" s="28">
+        <v>266.45</v>
+      </c>
+      <c r="H217" s="29">
+        <f t="shared" si="14"/>
+        <v>-6.6999999999999886</v>
+      </c>
+      <c r="I217" s="28">
+        <v>254.83</v>
+      </c>
+      <c r="J217" s="29">
+        <f t="shared" si="15"/>
+        <v>-18.319999999999965</v>
+      </c>
+      <c r="K217" s="46"/>
+      <c r="L217" s="47"/>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E218" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F218" s="44"/>
+      <c r="G218" s="28">
+        <v>266.45999999999998</v>
+      </c>
+      <c r="H218" s="29">
+        <f t="shared" si="14"/>
+        <v>-6.6899999999999977</v>
+      </c>
+      <c r="I218" s="28">
+        <v>254.84</v>
+      </c>
+      <c r="J218" s="29">
+        <f t="shared" si="15"/>
+        <v>-18.309999999999974</v>
+      </c>
+      <c r="K218" s="46"/>
+      <c r="L218" s="47"/>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E219" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F219" s="44"/>
+      <c r="G219" s="28">
+        <v>337.85</v>
+      </c>
+      <c r="H219" s="29">
+        <f t="shared" si="14"/>
+        <v>64.700000000000045</v>
+      </c>
+      <c r="I219" s="28">
+        <v>329.18</v>
+      </c>
+      <c r="J219" s="29">
+        <f t="shared" si="15"/>
+        <v>56.03000000000003</v>
+      </c>
+      <c r="K219" s="46"/>
+      <c r="L219" s="47"/>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E220" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F220" s="44"/>
+      <c r="G220" s="28">
+        <v>331.23</v>
+      </c>
+      <c r="H220" s="29">
+        <f t="shared" si="14"/>
+        <v>58.080000000000041</v>
+      </c>
+      <c r="I220" s="28">
+        <v>322.47000000000003</v>
+      </c>
+      <c r="J220" s="29">
+        <f t="shared" si="15"/>
+        <v>49.32000000000005</v>
+      </c>
+      <c r="K220" s="46"/>
+      <c r="L220" s="47"/>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E221" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F221" s="44"/>
+      <c r="G221" s="28">
+        <v>262.66000000000003</v>
+      </c>
+      <c r="H221" s="29">
+        <f t="shared" si="14"/>
+        <v>-10.489999999999952</v>
+      </c>
+      <c r="I221" s="28">
+        <v>250.51</v>
+      </c>
+      <c r="J221" s="29">
+        <f t="shared" si="15"/>
+        <v>-22.639999999999986</v>
+      </c>
+      <c r="K221" s="46"/>
+      <c r="L221" s="47"/>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E222" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F222" s="44"/>
+      <c r="G222" s="30">
+        <v>261.74</v>
+      </c>
+      <c r="H222" s="29">
+        <f t="shared" si="14"/>
+        <v>-11.409999999999968</v>
+      </c>
+      <c r="I222" s="28">
+        <v>249.58</v>
+      </c>
+      <c r="J222" s="29">
+        <f t="shared" si="15"/>
+        <v>-23.569999999999965</v>
+      </c>
+      <c r="K222" s="46"/>
+      <c r="L222" s="47"/>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E223" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F223" s="44"/>
+      <c r="G223" s="30">
+        <v>261.74</v>
+      </c>
+      <c r="H223" s="29">
+        <f t="shared" si="14"/>
+        <v>-11.409999999999968</v>
+      </c>
+      <c r="I223" s="28">
+        <v>249.57</v>
+      </c>
+      <c r="J223" s="29">
+        <f t="shared" si="15"/>
+        <v>-23.579999999999984</v>
+      </c>
+      <c r="K223" s="46"/>
+      <c r="L223" s="47"/>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E224" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F224" s="44"/>
+      <c r="G224" s="28">
+        <v>261.72000000000003</v>
+      </c>
+      <c r="H224" s="29">
+        <f t="shared" si="14"/>
+        <v>-11.42999999999995</v>
+      </c>
+      <c r="I224" s="28">
+        <v>249.55</v>
+      </c>
+      <c r="J224" s="29">
+        <f t="shared" si="15"/>
+        <v>-23.599999999999966</v>
+      </c>
+      <c r="K224" s="46"/>
+      <c r="L224" s="47"/>
+    </row>
+    <row r="225" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E225" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F225" s="44"/>
+      <c r="G225" s="28">
+        <v>266.42</v>
+      </c>
+      <c r="H225" s="29">
+        <f t="shared" si="14"/>
+        <v>-6.7299999999999613</v>
+      </c>
+      <c r="I225" s="28">
+        <v>254.8</v>
+      </c>
+      <c r="J225" s="29">
+        <f t="shared" si="15"/>
+        <v>-18.349999999999966</v>
+      </c>
+      <c r="K225" s="46"/>
+      <c r="L225" s="47"/>
+    </row>
+    <row r="226" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E226" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F226" s="44"/>
+      <c r="G226" s="28">
+        <v>266.49</v>
+      </c>
+      <c r="H226" s="29">
+        <f t="shared" si="14"/>
+        <v>-6.6599999999999682</v>
+      </c>
+      <c r="I226" s="28">
+        <v>254.87</v>
+      </c>
+      <c r="J226" s="29">
+        <f t="shared" si="15"/>
+        <v>-18.279999999999973</v>
+      </c>
+      <c r="K226" s="46"/>
+      <c r="L226" s="47"/>
+    </row>
+    <row r="227" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E227" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F227" s="44"/>
+      <c r="G227" s="28">
+        <v>266.44</v>
+      </c>
+      <c r="H227" s="29">
+        <f t="shared" si="14"/>
+        <v>-6.7099999999999795</v>
+      </c>
+      <c r="I227" s="28">
+        <v>254.81</v>
+      </c>
+      <c r="J227" s="29">
+        <f t="shared" si="15"/>
+        <v>-18.339999999999975</v>
+      </c>
+      <c r="K227" s="46"/>
+      <c r="L227" s="47"/>
+    </row>
+    <row r="228" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E228" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F228" s="44"/>
+      <c r="G228" s="28">
+        <v>261.39</v>
+      </c>
+      <c r="H228" s="29">
+        <f t="shared" si="14"/>
+        <v>-11.759999999999991</v>
+      </c>
+      <c r="I228" s="28">
+        <v>249.25</v>
+      </c>
+      <c r="J228" s="29">
+        <f t="shared" si="15"/>
+        <v>-23.899999999999977</v>
+      </c>
+      <c r="K228" s="46"/>
+      <c r="L228" s="47"/>
+    </row>
+    <row r="229" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E229" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F229" s="44"/>
+      <c r="G229" s="28">
+        <v>261.37</v>
+      </c>
+      <c r="H229" s="29">
+        <f t="shared" si="14"/>
+        <v>-11.779999999999973</v>
+      </c>
+      <c r="I229" s="28">
+        <v>249.22</v>
+      </c>
+      <c r="J229" s="29">
+        <f t="shared" si="15"/>
+        <v>-23.929999999999978</v>
+      </c>
+      <c r="K229" s="46"/>
+      <c r="L229" s="47"/>
+    </row>
+    <row r="230" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E230" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F230" s="44"/>
+      <c r="G230" s="28">
+        <v>261.85000000000002</v>
+      </c>
+      <c r="H230" s="29">
+        <f t="shared" si="14"/>
+        <v>-11.299999999999955</v>
+      </c>
+      <c r="I230" s="28">
+        <v>249.65</v>
+      </c>
+      <c r="J230" s="29">
+        <f t="shared" si="15"/>
+        <v>-23.499999999999972</v>
+      </c>
+      <c r="K230" s="46"/>
+      <c r="L230" s="47"/>
+    </row>
+    <row r="231" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E231" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F231" s="44"/>
+      <c r="G231" s="28">
+        <v>261.82</v>
+      </c>
+      <c r="H231" s="29">
+        <f t="shared" si="14"/>
+        <v>-11.329999999999984</v>
+      </c>
+      <c r="I231" s="28">
+        <v>249.62</v>
+      </c>
+      <c r="J231" s="29">
+        <f t="shared" si="15"/>
+        <v>-23.529999999999973</v>
+      </c>
+      <c r="K231" s="46"/>
+      <c r="L231" s="47"/>
+    </row>
+    <row r="232" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E232" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F232" s="45"/>
+      <c r="G232" s="28">
+        <v>269.13</v>
+      </c>
+      <c r="H232" s="29">
+        <f t="shared" si="14"/>
+        <v>-4.0199999999999818</v>
+      </c>
+      <c r="I232" s="28">
+        <v>257.48</v>
+      </c>
+      <c r="J232" s="29">
+        <f t="shared" si="15"/>
+        <v>-15.669999999999959</v>
+      </c>
+      <c r="K232" s="46"/>
+      <c r="L232" s="47"/>
+    </row>
+    <row r="235" spans="5:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E235" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="236" spans="5:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="E236" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="237" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E237" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="238" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E238" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+    </row>
+    <row r="239" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E239" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="K239" s="1"/>
+      <c r="L239" s="1"/>
+    </row>
+    <row r="240" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E240" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F240" s="10"/>
+      <c r="G240" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="H240" s="42"/>
+      <c r="I240" s="42"/>
+      <c r="J240" s="42"/>
+      <c r="K240" s="1"/>
+      <c r="L240" s="1"/>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A241" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B241" s="35"/>
+      <c r="C241" s="35"/>
+      <c r="E241" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F241" s="43"/>
+      <c r="G241" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H241" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I241" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J241" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K241" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L241" s="38"/>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A242" s="35"/>
+      <c r="B242" s="35"/>
+      <c r="C242" s="35"/>
+      <c r="E242" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F242" s="44"/>
+      <c r="G242" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H242" s="31"/>
+      <c r="I242" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="J242" s="31"/>
+      <c r="K242" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="L242" s="47"/>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A243" s="35"/>
+      <c r="B243" s="35"/>
+      <c r="C243" s="35"/>
+      <c r="E243" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F243" s="44"/>
+      <c r="G243" s="28">
+        <v>304.11</v>
+      </c>
+      <c r="H243" s="29">
+        <f>G243-273.15</f>
+        <v>30.960000000000036</v>
+      </c>
+      <c r="I243" s="28"/>
+      <c r="J243" s="29">
+        <f>I243-273.15</f>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K243" s="46"/>
+      <c r="L243" s="47"/>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A244" s="35"/>
+      <c r="B244" s="35"/>
+      <c r="C244" s="35"/>
+      <c r="E244" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F244" s="44"/>
+      <c r="G244" s="28">
+        <v>304.12</v>
+      </c>
+      <c r="H244" s="29">
+        <f t="shared" ref="H244:H262" si="16">G244-273.15</f>
+        <v>30.970000000000027</v>
+      </c>
+      <c r="I244" s="28"/>
+      <c r="J244" s="29">
+        <f t="shared" ref="J244:J262" si="17">I244-273.15</f>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K244" s="46"/>
+      <c r="L244" s="47"/>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A245" s="35"/>
+      <c r="B245" s="35"/>
+      <c r="C245" s="35"/>
+      <c r="E245" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F245" s="44"/>
+      <c r="G245" s="28">
+        <v>304.02</v>
+      </c>
+      <c r="H245" s="29">
+        <f t="shared" si="16"/>
+        <v>30.870000000000005</v>
+      </c>
+      <c r="I245" s="28"/>
+      <c r="J245" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K245" s="46"/>
+      <c r="L245" s="47"/>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A246" s="35"/>
+      <c r="B246" s="35"/>
+      <c r="C246" s="35"/>
+      <c r="E246" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F246" s="44"/>
+      <c r="G246" s="28">
+        <v>304.04000000000002</v>
+      </c>
+      <c r="H246" s="29">
+        <f t="shared" si="16"/>
+        <v>30.890000000000043</v>
+      </c>
+      <c r="I246" s="28"/>
+      <c r="J246" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K246" s="46"/>
+      <c r="L246" s="47"/>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A247" s="35"/>
+      <c r="B247" s="35"/>
+      <c r="C247" s="35"/>
+      <c r="E247" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F247" s="44"/>
+      <c r="G247" s="28">
+        <v>304.02</v>
+      </c>
+      <c r="H247" s="29">
+        <f t="shared" si="16"/>
+        <v>30.870000000000005</v>
+      </c>
+      <c r="I247" s="28"/>
+      <c r="J247" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K247" s="46"/>
+      <c r="L247" s="47"/>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E248" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F248" s="44"/>
+      <c r="G248" s="28">
+        <v>304.04000000000002</v>
+      </c>
+      <c r="H248" s="29">
+        <f t="shared" si="16"/>
+        <v>30.890000000000043</v>
+      </c>
+      <c r="I248" s="28"/>
+      <c r="J248" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K248" s="46"/>
+      <c r="L248" s="47"/>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E249" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F249" s="44"/>
+      <c r="G249" s="28">
+        <v>359.88</v>
+      </c>
+      <c r="H249" s="29">
+        <f t="shared" si="16"/>
+        <v>86.730000000000018</v>
+      </c>
+      <c r="I249" s="28"/>
+      <c r="J249" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K249" s="46"/>
+      <c r="L249" s="47"/>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E250" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F250" s="44"/>
+      <c r="G250" s="28">
+        <v>353.36</v>
+      </c>
+      <c r="H250" s="29">
+        <f t="shared" si="16"/>
+        <v>80.210000000000036</v>
+      </c>
+      <c r="I250" s="28"/>
+      <c r="J250" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K250" s="46"/>
+      <c r="L250" s="47"/>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E251" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F251" s="44"/>
+      <c r="G251" s="28">
+        <v>301.43</v>
+      </c>
+      <c r="H251" s="29">
+        <f t="shared" si="16"/>
+        <v>28.28000000000003</v>
+      </c>
+      <c r="I251" s="28"/>
+      <c r="J251" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K251" s="46"/>
+      <c r="L251" s="47"/>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E252" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F252" s="44"/>
+      <c r="G252" s="30">
+        <v>300.68</v>
+      </c>
+      <c r="H252" s="29">
+        <f t="shared" si="16"/>
+        <v>27.53000000000003</v>
+      </c>
+      <c r="I252" s="28"/>
+      <c r="J252" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K252" s="46"/>
+      <c r="L252" s="47"/>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E253" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F253" s="44"/>
+      <c r="G253" s="30">
+        <v>300.67</v>
+      </c>
+      <c r="H253" s="29">
+        <f t="shared" si="16"/>
+        <v>27.520000000000039</v>
+      </c>
+      <c r="I253" s="28"/>
+      <c r="J253" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K253" s="46"/>
+      <c r="L253" s="47"/>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E254" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F254" s="44"/>
+      <c r="G254" s="28">
+        <v>300.64999999999998</v>
+      </c>
+      <c r="H254" s="29">
+        <f t="shared" si="16"/>
+        <v>27.5</v>
+      </c>
+      <c r="I254" s="28"/>
+      <c r="J254" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K254" s="46"/>
+      <c r="L254" s="47"/>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E255" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F255" s="44"/>
+      <c r="G255" s="28">
+        <v>303.99</v>
+      </c>
+      <c r="H255" s="29">
+        <f t="shared" si="16"/>
+        <v>30.840000000000032</v>
+      </c>
+      <c r="I255" s="28"/>
+      <c r="J255" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K255" s="46"/>
+      <c r="L255" s="47"/>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E256" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F256" s="44"/>
+      <c r="G256" s="28">
+        <v>304.06</v>
+      </c>
+      <c r="H256" s="29">
+        <f t="shared" si="16"/>
+        <v>30.910000000000025</v>
+      </c>
+      <c r="I256" s="28"/>
+      <c r="J256" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K256" s="46"/>
+      <c r="L256" s="47"/>
+    </row>
+    <row r="257" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E257" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F257" s="44"/>
+      <c r="G257" s="28">
+        <v>304.01</v>
+      </c>
+      <c r="H257" s="29">
+        <f t="shared" si="16"/>
+        <v>30.860000000000014</v>
+      </c>
+      <c r="I257" s="28"/>
+      <c r="J257" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K257" s="46"/>
+      <c r="L257" s="47"/>
+    </row>
+    <row r="258" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E258" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F258" s="44"/>
+      <c r="G258" s="28">
+        <v>300.33999999999997</v>
+      </c>
+      <c r="H258" s="29">
+        <f t="shared" si="16"/>
+        <v>27.189999999999998</v>
+      </c>
+      <c r="I258" s="28"/>
+      <c r="J258" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K258" s="46"/>
+      <c r="L258" s="47"/>
+    </row>
+    <row r="259" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E259" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F259" s="44"/>
+      <c r="G259" s="28">
+        <v>300.31</v>
+      </c>
+      <c r="H259" s="29">
+        <f t="shared" si="16"/>
+        <v>27.160000000000025</v>
+      </c>
+      <c r="I259" s="28"/>
+      <c r="J259" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K259" s="46"/>
+      <c r="L259" s="47"/>
+    </row>
+    <row r="260" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E260" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F260" s="44"/>
+      <c r="G260" s="28">
+        <v>300.76</v>
+      </c>
+      <c r="H260" s="29">
+        <f t="shared" si="16"/>
+        <v>27.610000000000014</v>
+      </c>
+      <c r="I260" s="28"/>
+      <c r="J260" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K260" s="46"/>
+      <c r="L260" s="47"/>
+    </row>
+    <row r="261" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E261" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F261" s="44"/>
+      <c r="G261" s="28">
+        <v>300.73</v>
+      </c>
+      <c r="H261" s="29">
+        <f t="shared" si="16"/>
+        <v>27.580000000000041</v>
+      </c>
+      <c r="I261" s="28"/>
+      <c r="J261" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K261" s="46"/>
+      <c r="L261" s="47"/>
+    </row>
+    <row r="262" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E262" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F262" s="45"/>
+      <c r="G262" s="28">
+        <v>306.16000000000003</v>
+      </c>
+      <c r="H262" s="29">
+        <f t="shared" si="16"/>
+        <v>33.010000000000048</v>
+      </c>
+      <c r="I262" s="28"/>
+      <c r="J262" s="29">
+        <f t="shared" si="17"/>
+        <v>-273.14999999999998</v>
+      </c>
+      <c r="K262" s="46"/>
+      <c r="L262" s="47"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="63">
+    <mergeCell ref="G240:J240"/>
+    <mergeCell ref="A241:C247"/>
+    <mergeCell ref="F241:F262"/>
+    <mergeCell ref="K241:L241"/>
+    <mergeCell ref="G242:H242"/>
+    <mergeCell ref="I242:J242"/>
+    <mergeCell ref="K242:L262"/>
+    <mergeCell ref="G210:J210"/>
+    <mergeCell ref="A211:C217"/>
+    <mergeCell ref="F211:F232"/>
+    <mergeCell ref="K211:L211"/>
+    <mergeCell ref="G212:H212"/>
+    <mergeCell ref="I212:J212"/>
+    <mergeCell ref="K212:L232"/>
+    <mergeCell ref="G180:J180"/>
+    <mergeCell ref="A181:C187"/>
+    <mergeCell ref="F181:F202"/>
+    <mergeCell ref="K181:L181"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="I182:J182"/>
+    <mergeCell ref="K182:L202"/>
     <mergeCell ref="G150:J150"/>
     <mergeCell ref="A151:C157"/>
     <mergeCell ref="F151:F172"/>
@@ -9091,55 +10772,55 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:N21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" customWidth="1"/>
-    <col min="11" max="13" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" customWidth="1"/>
+    <col min="11" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="48" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="48"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E12" s="48" t="s">
         <v>49</v>
       </c>
@@ -9167,35 +10848,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E13" s="48" t="s">
         <v>56</v>
       </c>
       <c r="F13" s="48"/>
       <c r="G13" s="48"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E15" s="48" t="s">
         <v>57</v>
       </c>
       <c r="F15" s="48"/>
       <c r="G15" s="48"/>
     </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E17" s="48" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="48"/>
       <c r="G17" s="48"/>
     </row>
-    <row r="19" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E19" s="48" t="s">
         <v>58</v>
       </c>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
     </row>
-    <row r="21" spans="5:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E21" s="48" t="s">
         <v>59</v>
       </c>
@@ -9217,28 +10898,28 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:U44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="19"/>
       <c r="B2" s="22" t="s">
         <v>77</v>
@@ -9292,7 +10973,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>77</v>
       </c>
@@ -9348,7 +11029,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>78</v>
       </c>
@@ -9404,7 +11085,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>79</v>
       </c>
@@ -9460,7 +11141,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>80</v>
       </c>
@@ -9516,7 +11197,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>81</v>
       </c>
@@ -9572,7 +11253,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>82</v>
       </c>
@@ -9628,7 +11309,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>83</v>
       </c>
@@ -9684,7 +11365,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>84</v>
       </c>
@@ -9740,7 +11421,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>85</v>
       </c>
@@ -9796,7 +11477,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>86</v>
       </c>
@@ -9852,7 +11533,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>87</v>
       </c>
@@ -9908,7 +11589,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>64</v>
       </c>
@@ -9964,7 +11645,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>88</v>
       </c>
@@ -10020,7 +11701,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>89</v>
       </c>
@@ -10076,7 +11757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>90</v>
       </c>
@@ -10132,7 +11813,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>91</v>
       </c>
@@ -10188,7 +11869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>92</v>
       </c>
@@ -10244,7 +11925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="19"/>
       <c r="B24" s="22" t="s">
         <v>77</v>
@@ -10307,7 +11988,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>77</v>
       </c>
@@ -10372,7 +12053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>78</v>
       </c>
@@ -10437,7 +12118,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>79</v>
       </c>
@@ -10502,7 +12183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>80</v>
       </c>
@@ -10567,7 +12248,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>81</v>
       </c>
@@ -10632,7 +12313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
         <v>82</v>
       </c>
@@ -10697,7 +12378,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>99</v>
       </c>
@@ -10758,7 +12439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
         <v>100</v>
       </c>
@@ -10819,7 +12500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
         <v>101</v>
       </c>
@@ -10880,7 +12561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
         <v>83</v>
       </c>
@@ -10945,7 +12626,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
         <v>84</v>
       </c>
@@ -11010,7 +12691,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
         <v>85</v>
       </c>
@@ -11075,7 +12756,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
         <v>86</v>
       </c>
@@ -11140,7 +12821,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
         <v>87</v>
       </c>
@@ -11199,7 +12880,7 @@
       <c r="T38" s="25"/>
       <c r="U38" s="25"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
         <v>64</v>
       </c>
@@ -11258,7 +12939,7 @@
       <c r="T39" s="25"/>
       <c r="U39" s="25"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>88</v>
       </c>
@@ -11323,7 +13004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
         <v>89</v>
       </c>
@@ -11388,7 +13069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
         <v>90</v>
       </c>
@@ -11453,7 +13134,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
         <v>91</v>
       </c>
@@ -11518,7 +13199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
         <v>92</v>
       </c>
